--- a/src/main/java/TestSuite/TestCase.xlsx
+++ b/src/main/java/TestSuite/TestCase.xlsx
@@ -4,17 +4,32 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29420" windowHeight="14700" tabRatio="851"/>
+    <workbookView windowWidth="29420" windowHeight="15520" tabRatio="851"/>
   </bookViews>
   <sheets>
     <sheet name="JKNS" sheetId="9" r:id="rId1"/>
+    <sheet name="Workperx" sheetId="10" r:id="rId2"/>
+    <sheet name="PhonePe" sheetId="12" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="226">
   <si>
     <t>description</t>
   </si>
@@ -49,7 +64,7 @@
     <t>navigate1</t>
   </si>
   <si>
-    <t>https://app.lifafa.team/in/jai_kisaan_navratna_sambandh</t>
+    <t>https://lifafa-team.webflow.io/jkns</t>
   </si>
   <si>
     <t>Verify URL</t>
@@ -58,32 +73,653 @@
     <t>verifyurl</t>
   </si>
   <si>
-    <t>Click on usericon</t>
+    <t>Switch to Iframe</t>
+  </si>
+  <si>
+    <t>iframe</t>
+  </si>
+  <si>
+    <t>jknsLoginFrame</t>
+  </si>
+  <si>
+    <t>Enter Phone Number</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>9876543210</t>
+  </si>
+  <si>
+    <t>phonenumber</t>
+  </si>
+  <si>
+    <t>Click on Proceed</t>
   </si>
   <si>
     <t>click1</t>
   </si>
   <si>
-    <t>usericon</t>
+    <t>proceed</t>
+  </si>
+  <si>
+    <t>Enter OTP</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>loginotpverification</t>
+  </si>
+  <si>
+    <t>Click on Home Button</t>
+  </si>
+  <si>
+    <t>navigate2</t>
+  </si>
+  <si>
+    <t>https://portal.lifafa.team/store/inbom240400012s04/home</t>
+  </si>
+  <si>
+    <t>Click on PPC</t>
+  </si>
+  <si>
+    <t>scroll2</t>
+  </si>
+  <si>
+    <t>ppcviewall</t>
+  </si>
+  <si>
+    <t>Click on Virtual Yes Bank</t>
+  </si>
+  <si>
+    <t>virtualyesbankppc</t>
+  </si>
+  <si>
+    <t>Enter Dynamic Value</t>
+  </si>
+  <si>
+    <t>500</t>
+  </si>
+  <si>
+    <t>enterdynamicvalue</t>
+  </si>
+  <si>
+    <t>Add Denomination</t>
+  </si>
+  <si>
+    <t>add-dynamic-denomination</t>
+  </si>
+  <si>
+    <t>Click on continue</t>
+  </si>
+  <si>
+    <t>gcmcontinue</t>
+  </si>
+  <si>
+    <t>Click on terms of use</t>
+  </si>
+  <si>
+    <t>ppc-termofuse</t>
+  </si>
+  <si>
+    <t>Click on buy gift card</t>
+  </si>
+  <si>
+    <t>buyppc</t>
+  </si>
+  <si>
+    <t>Click on User KYC Pending</t>
+  </si>
+  <si>
+    <t>completekyc</t>
+  </si>
+  <si>
+    <t>User KYC acknowledge</t>
+  </si>
+  <si>
+    <t>userkycacknowledge</t>
+  </si>
+  <si>
+    <t>Scroll Page</t>
+  </si>
+  <si>
+    <t>scroll1</t>
+  </si>
+  <si>
+    <t>Click on continue button</t>
+  </si>
+  <si>
+    <t>userkyc-continue</t>
+  </si>
+  <si>
+    <t>Enter Aadhaar number</t>
+  </si>
+  <si>
+    <t>999988887777</t>
+  </si>
+  <si>
+    <t>enteraadhaarnumber</t>
+  </si>
+  <si>
+    <t>aadhaarnumbercontinue</t>
+  </si>
+  <si>
+    <t>Enter Aadhaar number OTP</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>aadhaarnumberotp</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar number OTP</t>
+  </si>
+  <si>
+    <t>verifyaadhaarotp</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar number</t>
+  </si>
+  <si>
+    <t>verifyeditbox</t>
+  </si>
+  <si>
+    <t>verifyaadhaarnumber</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar name</t>
+  </si>
+  <si>
+    <t>Dummy User</t>
+  </si>
+  <si>
+    <t>verifyaadhaarname</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar DOB</t>
+  </si>
+  <si>
+    <t>verifyaadhaardob</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar Care of</t>
+  </si>
+  <si>
+    <t>verifyaadhaarfathername</t>
+  </si>
+  <si>
+    <t>Verify Aadhaar Address</t>
+  </si>
+  <si>
+    <t>verifyaadhaaraddress</t>
+  </si>
+  <si>
+    <t>Click on confirm button</t>
+  </si>
+  <si>
+    <t>confirmaadhaar</t>
+  </si>
+  <si>
+    <t>Enter PAN number OTP</t>
+  </si>
+  <si>
+    <t>AAAAA1111A</t>
+  </si>
+  <si>
+    <t>enterpannumber</t>
+  </si>
+  <si>
+    <t>pannumbercontinue</t>
+  </si>
+  <si>
+    <t>Open Selfie camera</t>
+  </si>
+  <si>
+    <t>userselfiecamera</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Upload Selfie</t>
+  </si>
+  <si>
+    <t>src/main/java/Files/success.png</t>
+  </si>
+  <si>
+    <t>uploadselfie</t>
+  </si>
+  <si>
+    <t>userkyc-complete-continue</t>
+  </si>
+  <si>
+    <t>Click on Vehicle view all</t>
+  </si>
+  <si>
+    <t>vehicleviewall</t>
+  </si>
+  <si>
+    <t>Enter Address Line 1</t>
+  </si>
+  <si>
+    <t>Jp Nagar</t>
+  </si>
+  <si>
+    <t>enteraddressline1</t>
+  </si>
+  <si>
+    <t>Enter Address Line 2</t>
+  </si>
+  <si>
+    <t>4th Phase</t>
+  </si>
+  <si>
+    <t>enteraddressline2</t>
+  </si>
+  <si>
+    <t>Enter City</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>entercity</t>
+  </si>
+  <si>
+    <t>Enter State</t>
+  </si>
+  <si>
+    <t>Karnataka</t>
+  </si>
+  <si>
+    <t>enterstate</t>
+  </si>
+  <si>
+    <t>Enter Zip Code</t>
+  </si>
+  <si>
+    <t>560078</t>
+  </si>
+  <si>
+    <t>enterzipcode</t>
+  </si>
+  <si>
+    <t>Enter Country</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>entercountry</t>
+  </si>
+  <si>
+    <t>vehicle-termofuse</t>
+  </si>
+  <si>
+    <t>buyvehicle</t>
+  </si>
+  <si>
+    <t>Click on Company KYC Pending</t>
+  </si>
+  <si>
+    <t>Company KYC acknowledge</t>
+  </si>
+  <si>
+    <t>companykycacknowledge</t>
+  </si>
+  <si>
+    <t>companykyc-continue</t>
+  </si>
+  <si>
+    <t>Enter iFMS Code</t>
+  </si>
+  <si>
+    <t>LTSPL</t>
+  </si>
+  <si>
+    <t>enterifmscode</t>
+  </si>
+  <si>
+    <t>ifmscontinue</t>
+  </si>
+  <si>
+    <t>companyselfiecamera</t>
+  </si>
+  <si>
+    <t>uplaodifms</t>
+  </si>
+  <si>
+    <t>companykyc-complete-continue</t>
+  </si>
+  <si>
+    <t>gcmviewall</t>
+  </si>
+  <si>
+    <t>Click on Ecommerce view all</t>
+  </si>
+  <si>
+    <t>ecommerceviewall</t>
+  </si>
+  <si>
+    <t>Click on Flipkart</t>
+  </si>
+  <si>
+    <t>flipkartgc</t>
+  </si>
+  <si>
+    <t>Select denomination</t>
+  </si>
+  <si>
+    <t>2nd-denomination</t>
+  </si>
+  <si>
+    <t>3rd-denomination</t>
+  </si>
+  <si>
+    <t>Click on Wallet pay button</t>
+  </si>
+  <si>
+    <t>click2</t>
+  </si>
+  <si>
+    <t>walletpay</t>
+  </si>
+  <si>
+    <t>Click on Wallet redeem button</t>
+  </si>
+  <si>
+    <t>walletredeemotp</t>
+  </si>
+  <si>
+    <t>Click on Wallet confirm button</t>
+  </si>
+  <si>
+    <t>walletconfirmotp</t>
+  </si>
+  <si>
+    <t>Capture payment success</t>
+  </si>
+  <si>
+    <t>capture1</t>
+  </si>
+  <si>
+    <t>Click on view orders</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s04-01/myaccount/gift-card</t>
+  </si>
+  <si>
+    <t>Capture GC details</t>
+  </si>
+  <si>
+    <t>capture2</t>
+  </si>
+  <si>
+    <t>Click on PPC view all</t>
+  </si>
+  <si>
+    <t>Click on NB Payment Mode</t>
+  </si>
+  <si>
+    <t>nbpayment</t>
+  </si>
+  <si>
+    <t>Click on select bank list</t>
+  </si>
+  <si>
+    <t>Axis</t>
+  </si>
+  <si>
+    <t>clickbanklist</t>
+  </si>
+  <si>
+    <t>Click on select bank</t>
+  </si>
+  <si>
+    <t>selectbank</t>
+  </si>
+  <si>
+    <t>Click on NB Pay</t>
+  </si>
+  <si>
+    <t>nbpay</t>
+  </si>
+  <si>
+    <t>Enter NB username</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>nbusername</t>
+  </si>
+  <si>
+    <t>Enter NB password</t>
+  </si>
+  <si>
+    <t>nbpwd</t>
+  </si>
+  <si>
+    <t>Click on login button</t>
+  </si>
+  <si>
+    <t>nblogin</t>
+  </si>
+  <si>
+    <t>Handle the alert box</t>
+  </si>
+  <si>
+    <t>alert</t>
+  </si>
+  <si>
+    <t>nbconfirm</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s04/myaccount/cash-cards</t>
+  </si>
+  <si>
+    <t>Click on pending orders</t>
+  </si>
+  <si>
+    <t>pendingorders</t>
+  </si>
+  <si>
+    <t>Click on continue payment</t>
+  </si>
+  <si>
+    <t>lowbalancepopupok</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s04/myaccount/products</t>
+  </si>
+  <si>
+    <t>Click on Myaccount</t>
+  </si>
+  <si>
+    <t>myaccount</t>
+  </si>
+  <si>
+    <t>Click on Logout</t>
+  </si>
+  <si>
+    <t>logout</t>
+  </si>
+  <si>
+    <t>Click on Logout yes</t>
+  </si>
+  <si>
+    <t>logoutyes</t>
   </si>
   <si>
     <t>Close the browser</t>
   </si>
   <si>
     <t>close</t>
+  </si>
+  <si>
+    <t>https://lifafa-team.webflow.io/workperx</t>
+  </si>
+  <si>
+    <t>Click on Login</t>
+  </si>
+  <si>
+    <t>workperxlogin</t>
+  </si>
+  <si>
+    <t>Enter Email</t>
+  </si>
+  <si>
+    <t>dummyuser@lifafa.com</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>workperxproceed</t>
+  </si>
+  <si>
+    <t>Click on Vouchers</t>
+  </si>
+  <si>
+    <t>vouchers</t>
+  </si>
+  <si>
+    <t>workperxecommerceviewall</t>
+  </si>
+  <si>
+    <t>workperxflipkartgc</t>
+  </si>
+  <si>
+    <t>workperxnb</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s02/myaccount/gift-card</t>
+  </si>
+  <si>
+    <t>https://portal.lifafa.team/store/inbom240400012s02/home</t>
+  </si>
+  <si>
+    <t>Click on LTA</t>
+  </si>
+  <si>
+    <t>lta</t>
+  </si>
+  <si>
+    <t>Click on Travel</t>
+  </si>
+  <si>
+    <t>travel</t>
+  </si>
+  <si>
+    <t>Click on ClearTrip GC</t>
+  </si>
+  <si>
+    <t>workperxtravelcleartrip</t>
+  </si>
+  <si>
+    <t>Click on Deals</t>
+  </si>
+  <si>
+    <t>workperxdeals</t>
+  </si>
+  <si>
+    <t>Click on Send as a gift</t>
+  </si>
+  <si>
+    <t>Sendasagift</t>
+  </si>
+  <si>
+    <t>Enter Reciever First Name</t>
+  </si>
+  <si>
+    <t>Nikhil</t>
+  </si>
+  <si>
+    <t>Sendgcfirstname</t>
+  </si>
+  <si>
+    <t>Enter Reciever Last Name</t>
+  </si>
+  <si>
+    <t>Kumar</t>
+  </si>
+  <si>
+    <t>Sendgclastname</t>
+  </si>
+  <si>
+    <t>Enter Reciever Email</t>
+  </si>
+  <si>
+    <t>Nikhil.kumar@lifafa.com</t>
+  </si>
+  <si>
+    <t>Sendgcemail</t>
+  </si>
+  <si>
+    <t>Enter Reciever Phone Number</t>
+  </si>
+  <si>
+    <t>9108136936</t>
+  </si>
+  <si>
+    <t>Sendphonenumber</t>
+  </si>
+  <si>
+    <t>Select theme</t>
+  </si>
+  <si>
+    <t>Sendtheme</t>
+  </si>
+  <si>
+    <t>Enter Message</t>
+  </si>
+  <si>
+    <t>Automation Testing!</t>
+  </si>
+  <si>
+    <t>Sendmessage</t>
+  </si>
+  <si>
+    <t>gc-termofuse</t>
+  </si>
+  <si>
+    <t>buygiftcard</t>
+  </si>
+  <si>
+    <t>dealsnb</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s02/myaccount</t>
+  </si>
+  <si>
+    <t>https://lifafa-team.webflow.io/phonepe-apple-store</t>
+  </si>
+  <si>
+    <t>phonepeLoginFrame</t>
+  </si>
+  <si>
+    <t>https://portal.lifafa.team/store/inbom240400012s05/home</t>
+  </si>
+  <si>
+    <t>imagineapple</t>
+  </si>
+  <si>
+    <t>https://store.lifafa.team/inbom240400012s05/myaccount/gift-card</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,19 +740,13 @@
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -137,25 +767,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -174,8 +806,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -190,49 +846,37 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -245,7 +889,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -257,49 +919,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,43 +955,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,7 +979,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -377,7 +997,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -389,7 +1033,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +1045,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,19 +1069,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -436,30 +1080,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -482,18 +1102,46 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -513,25 +1161,21 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -539,203 +1183,211 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="48"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="60% - Accent6" xfId="1" builtinId="52"/>
-    <cellStyle name="40% - Accent6" xfId="2" builtinId="51"/>
-    <cellStyle name="60% - Accent5" xfId="3" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="4" builtinId="49"/>
-    <cellStyle name="40% - Accent5" xfId="5" builtinId="47"/>
-    <cellStyle name="20% - Accent5" xfId="6" builtinId="46"/>
-    <cellStyle name="60% - Accent4" xfId="7" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="8" builtinId="45"/>
-    <cellStyle name="40% - Accent4" xfId="9" builtinId="43"/>
-    <cellStyle name="Accent4" xfId="10" builtinId="41"/>
-    <cellStyle name="Linked Cell" xfId="11" builtinId="24"/>
-    <cellStyle name="40% - Accent3" xfId="12" builtinId="39"/>
-    <cellStyle name="60% - Accent2" xfId="13" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="14" builtinId="37"/>
-    <cellStyle name="40% - Accent2" xfId="15" builtinId="35"/>
-    <cellStyle name="20% - Accent2" xfId="16" builtinId="34"/>
-    <cellStyle name="Accent2" xfId="17" builtinId="33"/>
-    <cellStyle name="40% - Accent1" xfId="18" builtinId="31"/>
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30"/>
-    <cellStyle name="Accent1" xfId="20" builtinId="29"/>
-    <cellStyle name="Neutral" xfId="21" builtinId="28"/>
-    <cellStyle name="60% - Accent1" xfId="22" builtinId="32"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
     <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="20% - Accent4" xfId="24" builtinId="42"/>
-    <cellStyle name="Total" xfId="25" builtinId="25"/>
-    <cellStyle name="Output" xfId="26" builtinId="21"/>
-    <cellStyle name="Currency" xfId="27" builtinId="4"/>
-    <cellStyle name="20% - Accent3" xfId="28" builtinId="38"/>
-    <cellStyle name="Note" xfId="29" builtinId="10"/>
-    <cellStyle name="Input" xfId="30" builtinId="20"/>
-    <cellStyle name="Heading 4" xfId="31" builtinId="19"/>
-    <cellStyle name="Calculation" xfId="32" builtinId="22"/>
-    <cellStyle name="Good" xfId="33" builtinId="26"/>
-    <cellStyle name="Heading 3" xfId="34" builtinId="18"/>
-    <cellStyle name="CExplanatory Text" xfId="35" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="36" builtinId="16"/>
-    <cellStyle name="Comma [0]" xfId="37" builtinId="6"/>
-    <cellStyle name="20% - Accent6" xfId="38" builtinId="50"/>
-    <cellStyle name="Title" xfId="39" builtinId="15"/>
-    <cellStyle name="Currency [0]" xfId="40" builtinId="7"/>
-    <cellStyle name="Warning Text" xfId="41" builtinId="11"/>
-    <cellStyle name="Followed Hyperlink" xfId="42" builtinId="9"/>
-    <cellStyle name="Heading 2" xfId="43" builtinId="17"/>
-    <cellStyle name="Comma" xfId="44" builtinId="3"/>
-    <cellStyle name="Check Cell" xfId="45" builtinId="23"/>
-    <cellStyle name="60% - Accent3" xfId="46" builtinId="40"/>
-    <cellStyle name="Percent" xfId="47" builtinId="5"/>
-    <cellStyle name="Hyperlink" xfId="48" builtinId="8"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
@@ -1033,13 +1685,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E120"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="25.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="46.6640625" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="1" max="1" width="28.875" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="61.0625" customWidth="1"/>
+    <col min="4" max="4" width="28.875" customWidth="1"/>
+    <col min="5" max="5" width="8.5625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1083,7 +1736,7 @@
       <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D3" t="s">
@@ -1100,7 +1753,7 @@
       <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
@@ -1117,11 +1770,11 @@
       <c r="B5" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>7</v>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1134,19 +1787,3953 @@
       <c r="B6" t="s">
         <v>18</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>63</v>
+      </c>
+      <c r="B26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>64</v>
+      </c>
+      <c r="C28" s="7"/>
+      <c r="D28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>71</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>73</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" t="s">
+        <v>75</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" t="s">
+        <v>78</v>
+      </c>
+      <c r="D32" t="s">
+        <v>79</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="s">
+        <v>80</v>
+      </c>
+      <c r="E33" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>81</v>
+      </c>
+      <c r="B34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>84</v>
+      </c>
+      <c r="B35" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>87</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>27</v>
+      </c>
+      <c r="B37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>90</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>91</v>
+      </c>
+      <c r="D39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>93</v>
+      </c>
+      <c r="B40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>96</v>
+      </c>
+      <c r="B41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" t="s">
+        <v>97</v>
+      </c>
+      <c r="D41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" t="s">
+        <v>100</v>
+      </c>
+      <c r="D42" t="s">
+        <v>101</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>102</v>
+      </c>
+      <c r="B43" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D43" t="s">
+        <v>104</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>105</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D44" t="s">
+        <v>107</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" t="s">
+        <v>108</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>22</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" t="s">
+        <v>109</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" t="s">
+        <v>47</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>111</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>7</v>
+      </c>
+      <c r="D49" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>115</v>
+      </c>
+      <c r="D50" t="s">
+        <v>116</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>52</v>
+      </c>
+      <c r="B51" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C52" t="s">
+        <v>85</v>
+      </c>
+      <c r="D52" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>84</v>
+      </c>
+      <c r="B53" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>119</v>
+      </c>
+      <c r="E53" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>121</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>122</v>
+      </c>
+      <c r="B56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>123</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>124</v>
+      </c>
+      <c r="B57" t="s">
+        <v>22</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>125</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>126</v>
+      </c>
+      <c r="B58" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" t="s">
+        <v>127</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>126</v>
+      </c>
+      <c r="B59" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" t="s">
+        <v>7</v>
+      </c>
+      <c r="D59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" t="s">
+        <v>41</v>
+      </c>
+      <c r="E60" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="s">
+        <v>43</v>
+      </c>
+      <c r="E61" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" t="s">
+        <v>44</v>
+      </c>
+      <c r="B62" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="s">
+        <v>45</v>
+      </c>
+      <c r="E62" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" t="s">
+        <v>129</v>
+      </c>
+      <c r="B63" t="s">
+        <v>130</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" t="s">
+        <v>132</v>
+      </c>
+      <c r="B64" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D64" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" t="s">
+        <v>134</v>
+      </c>
+      <c r="B65" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="s">
+        <v>135</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" t="s">
+        <v>136</v>
+      </c>
+      <c r="B66" t="s">
+        <v>137</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="s">
+        <v>7</v>
+      </c>
+      <c r="E66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" t="s">
+        <v>10</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D67" t="s">
+        <v>7</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>140</v>
+      </c>
+      <c r="B68" t="s">
+        <v>141</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>27</v>
+      </c>
+      <c r="B69" t="s">
+        <v>28</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D69" t="s">
+        <v>7</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" t="s">
+        <v>142</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>32</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>34</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D72" t="s">
+        <v>37</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>39</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B74" t="s">
+        <v>41</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>42</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>43</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>45</v>
+      </c>
+      <c r="E76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" t="s">
+        <v>31</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>144</v>
+      </c>
+      <c r="E77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>145</v>
+      </c>
+      <c r="B78" t="s">
+        <v>18</v>
+      </c>
+      <c r="C78" t="s">
+        <v>146</v>
+      </c>
+      <c r="D78" t="s">
+        <v>147</v>
+      </c>
+      <c r="E78" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>149</v>
+      </c>
+      <c r="E79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>151</v>
+      </c>
+      <c r="E80" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" t="s">
+        <v>153</v>
+      </c>
+      <c r="D81" t="s">
+        <v>154</v>
+      </c>
+      <c r="E81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>155</v>
+      </c>
+      <c r="B82" t="s">
+        <v>18</v>
+      </c>
+      <c r="C82" t="s">
+        <v>153</v>
+      </c>
+      <c r="D82" t="s">
+        <v>156</v>
+      </c>
+      <c r="E82" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>157</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>158</v>
+      </c>
+      <c r="E83" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" t="s">
+        <v>160</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>7</v>
+      </c>
+      <c r="E84" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>75</v>
+      </c>
+      <c r="B85" t="s">
+        <v>22</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>161</v>
+      </c>
+      <c r="E85" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
+      <c r="A86" t="s">
+        <v>136</v>
+      </c>
+      <c r="B86" t="s">
+        <v>137</v>
+      </c>
+      <c r="C86" t="s">
+        <v>7</v>
+      </c>
+      <c r="D86" t="s">
+        <v>7</v>
+      </c>
+      <c r="E86" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
+      <c r="A87" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87" t="s">
+        <v>10</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D87" t="s">
+        <v>7</v>
+      </c>
+      <c r="E87" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
+      <c r="A88" t="s">
+        <v>163</v>
+      </c>
+      <c r="B88" t="s">
+        <v>130</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" t="s">
+        <v>164</v>
+      </c>
+      <c r="E88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
+      <c r="A89" t="s">
+        <v>140</v>
+      </c>
+      <c r="B89" t="s">
+        <v>141</v>
+      </c>
+      <c r="C89" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" t="s">
+        <v>7</v>
+      </c>
+      <c r="E89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
+      <c r="A90" t="s">
+        <v>27</v>
+      </c>
+      <c r="B90" t="s">
+        <v>28</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>7</v>
+      </c>
+      <c r="E90" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
+      <c r="A91" t="s">
+        <v>88</v>
+      </c>
+      <c r="B91" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>89</v>
+      </c>
+      <c r="E91" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
+      <c r="A92" t="s">
+        <v>90</v>
+      </c>
+      <c r="B92" t="s">
+        <v>18</v>
+      </c>
+      <c r="C92" t="s">
+        <v>91</v>
+      </c>
+      <c r="D92" t="s">
+        <v>92</v>
+      </c>
+      <c r="E92" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
+      <c r="A93" t="s">
+        <v>93</v>
+      </c>
+      <c r="B93" t="s">
+        <v>18</v>
+      </c>
+      <c r="C93" t="s">
+        <v>94</v>
+      </c>
+      <c r="D93" t="s">
+        <v>95</v>
+      </c>
+      <c r="E93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
+      <c r="A94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" t="s">
+        <v>18</v>
+      </c>
+      <c r="C94" t="s">
+        <v>97</v>
+      </c>
+      <c r="D94" t="s">
+        <v>98</v>
+      </c>
+      <c r="E94" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
+      <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" t="s">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>100</v>
+      </c>
+      <c r="D95" t="s">
+        <v>101</v>
+      </c>
+      <c r="E95" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>18</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D96" t="s">
+        <v>104</v>
+      </c>
+      <c r="E96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
+      <c r="A97" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" t="s">
+        <v>18</v>
+      </c>
+      <c r="C97" t="s">
+        <v>106</v>
+      </c>
+      <c r="D97" t="s">
+        <v>107</v>
+      </c>
+      <c r="E97" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
+      <c r="A98" t="s">
+        <v>42</v>
+      </c>
+      <c r="B98" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" t="s">
+        <v>7</v>
+      </c>
+      <c r="D98" t="s">
+        <v>108</v>
+      </c>
+      <c r="E98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
+      <c r="A99" t="s">
+        <v>44</v>
+      </c>
+      <c r="B99" t="s">
+        <v>22</v>
+      </c>
+      <c r="C99" t="s">
+        <v>7</v>
+      </c>
+      <c r="D99" t="s">
+        <v>109</v>
+      </c>
+      <c r="E99" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
+      <c r="A100" t="s">
+        <v>129</v>
+      </c>
+      <c r="B100" t="s">
+        <v>130</v>
+      </c>
+      <c r="C100" t="s">
+        <v>7</v>
+      </c>
+      <c r="D100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E100" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
+      <c r="A101" t="s">
+        <v>165</v>
+      </c>
+      <c r="B101" t="s">
+        <v>22</v>
+      </c>
+      <c r="C101" t="s">
+        <v>7</v>
+      </c>
+      <c r="D101" t="s">
+        <v>166</v>
+      </c>
+      <c r="E101" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
+      <c r="A102" t="s">
+        <v>132</v>
+      </c>
+      <c r="B102" t="s">
+        <v>18</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D102" t="s">
+        <v>133</v>
+      </c>
+      <c r="E102" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
+      <c r="A103" t="s">
+        <v>134</v>
+      </c>
+      <c r="B103" t="s">
+        <v>130</v>
+      </c>
+      <c r="C103" t="s">
+        <v>7</v>
+      </c>
+      <c r="D103" t="s">
+        <v>135</v>
+      </c>
+      <c r="E103" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
+      <c r="A104" t="s">
+        <v>143</v>
+      </c>
+      <c r="B104" t="s">
+        <v>31</v>
+      </c>
+      <c r="C104" t="s">
+        <v>7</v>
+      </c>
+      <c r="D104" t="s">
+        <v>144</v>
+      </c>
+      <c r="E104" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
+      <c r="A105" t="s">
+        <v>145</v>
+      </c>
+      <c r="B105" t="s">
+        <v>18</v>
+      </c>
+      <c r="C105" t="s">
+        <v>146</v>
+      </c>
+      <c r="D105" t="s">
+        <v>147</v>
+      </c>
+      <c r="E105" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
+      <c r="A106" t="s">
+        <v>148</v>
+      </c>
+      <c r="B106" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106" t="s">
+        <v>7</v>
+      </c>
+      <c r="D106" t="s">
+        <v>149</v>
+      </c>
+      <c r="E106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
+      <c r="A107" t="s">
+        <v>150</v>
+      </c>
+      <c r="B107" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" t="s">
+        <v>7</v>
+      </c>
+      <c r="D107" t="s">
+        <v>151</v>
+      </c>
+      <c r="E107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
+      <c r="A108" t="s">
+        <v>152</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" t="s">
+        <v>153</v>
+      </c>
+      <c r="D108" t="s">
+        <v>154</v>
+      </c>
+      <c r="E108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
+      <c r="A109" t="s">
+        <v>155</v>
+      </c>
+      <c r="B109" t="s">
+        <v>18</v>
+      </c>
+      <c r="C109" t="s">
+        <v>153</v>
+      </c>
+      <c r="D109" t="s">
+        <v>156</v>
+      </c>
+      <c r="E109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
+      <c r="A110" t="s">
+        <v>157</v>
+      </c>
+      <c r="B110" t="s">
+        <v>22</v>
+      </c>
+      <c r="C110" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" t="s">
+        <v>158</v>
+      </c>
+      <c r="E110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
+      <c r="A111" t="s">
+        <v>159</v>
+      </c>
+      <c r="B111" t="s">
+        <v>160</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D111" t="s">
+        <v>7</v>
+      </c>
+      <c r="E111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
+      <c r="A112" t="s">
+        <v>75</v>
+      </c>
+      <c r="B112" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D112" t="s">
+        <v>161</v>
+      </c>
+      <c r="E112" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
+      <c r="A113" t="s">
+        <v>136</v>
+      </c>
+      <c r="B113" t="s">
+        <v>137</v>
+      </c>
+      <c r="C113" t="s">
+        <v>7</v>
+      </c>
+      <c r="D113" t="s">
+        <v>7</v>
+      </c>
+      <c r="E113" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
+      <c r="A114" t="s">
+        <v>138</v>
+      </c>
+      <c r="B114" t="s">
+        <v>10</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D114" t="s">
+        <v>7</v>
+      </c>
+      <c r="E114" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
+      <c r="A115" t="s">
+        <v>140</v>
+      </c>
+      <c r="B115" t="s">
+        <v>141</v>
+      </c>
+      <c r="C115" t="s">
+        <v>7</v>
+      </c>
+      <c r="D115" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
+      <c r="A116" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" t="s">
+        <v>130</v>
+      </c>
+      <c r="C116" t="s">
+        <v>7</v>
+      </c>
+      <c r="D116" t="s">
+        <v>164</v>
+      </c>
+      <c r="E116" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
+      <c r="A117" t="s">
+        <v>168</v>
+      </c>
+      <c r="B117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" t="s">
+        <v>7</v>
+      </c>
+      <c r="D117" t="s">
+        <v>169</v>
+      </c>
+      <c r="E117" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
+      <c r="A118" t="s">
+        <v>170</v>
+      </c>
+      <c r="B118" t="s">
+        <v>22</v>
+      </c>
+      <c r="C118" t="s">
+        <v>7</v>
+      </c>
+      <c r="D118" t="s">
+        <v>171</v>
+      </c>
+      <c r="E118" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
+      <c r="A119" t="s">
+        <v>172</v>
+      </c>
+      <c r="B119" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" t="s">
+        <v>7</v>
+      </c>
+      <c r="D119" t="s">
+        <v>173</v>
+      </c>
+      <c r="E119" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
+      <c r="A120" t="s">
+        <v>174</v>
+      </c>
+      <c r="B120" t="s">
+        <v>175</v>
+      </c>
+      <c r="C120" t="s">
+        <v>7</v>
+      </c>
+      <c r="D120" t="s">
+        <v>7</v>
+      </c>
+      <c r="E120" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C67" r:id="rId1" display="https://store.lifafa.team/inbom240400012s04-01/myaccount/gift-card"/>
+    <hyperlink ref="C87" r:id="rId2" display="https://store.lifafa.team/inbom240400012s04/myaccount/cash-cards" tooltip="https://store.lifafa.team/inbom240400012s04/myaccount/cash-cards"/>
+    <hyperlink ref="C114" r:id="rId3" display="https://store.lifafa.team/inbom240400012s04/myaccount/products" tooltip="https://store.lifafa.team/inbom240400012s04/myaccount/products"/>
+    <hyperlink ref="C4" r:id="rId4" display="https://lifafa-team.webflow.io/jkns" tooltip="https://lifafa-team.webflow.io/jkns"/>
+    <hyperlink ref="C3" r:id="rId4" display="https://lifafa-team.webflow.io/jkns" tooltip="https://lifafa-team.webflow.io/jkns"/>
+    <hyperlink ref="C37" r:id="rId5" display="https://portal.lifafa.team/store/inbom240400012s04/home"/>
+    <hyperlink ref="C69" r:id="rId5" display="https://portal.lifafa.team/store/inbom240400012s04/home"/>
+    <hyperlink ref="C90" r:id="rId5" display="https://portal.lifafa.team/store/inbom240400012s04/home"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E85"/>
+  <sheetFormatPr defaultColWidth="55.7265625" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="35.6796875" customWidth="1"/>
+    <col min="2" max="2" width="34.765625" customWidth="1"/>
+    <col min="3" max="3" width="55.7265625" customWidth="1"/>
+    <col min="4" max="4" width="31.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.7578125" customWidth="1"/>
+    <col min="6" max="16384" width="55.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="1:5">
+      <c r="A19" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" spans="1:5">
+      <c r="A48" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>196</v>
+      </c>
+      <c r="B53" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" t="s">
+        <v>197</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>41</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>198</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B66" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="s">
+        <v>219</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>146</v>
+      </c>
+      <c r="D69" t="s">
+        <v>147</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" customFormat="1" spans="1:5">
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="s">
+        <v>149</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" t="s">
+        <v>150</v>
+      </c>
+      <c r="B71" t="s">
+        <v>22</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="s">
+        <v>151</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
+      <c r="A72" t="s">
+        <v>152</v>
+      </c>
+      <c r="B72" t="s">
+        <v>18</v>
+      </c>
+      <c r="C72" t="s">
+        <v>153</v>
+      </c>
+      <c r="D72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" t="s">
+        <v>155</v>
+      </c>
+      <c r="B73" t="s">
+        <v>18</v>
+      </c>
+      <c r="C73" t="s">
+        <v>153</v>
+      </c>
+      <c r="D73" t="s">
+        <v>156</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
+      <c r="A74" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="s">
+        <v>158</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
+      <c r="A75" t="s">
+        <v>159</v>
+      </c>
+      <c r="B75" t="s">
+        <v>160</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D75" t="s">
+        <v>7</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>22</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D76" t="s">
+        <v>161</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
+      <c r="A77" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" t="s">
+        <v>7</v>
+      </c>
+      <c r="D77" t="s">
+        <v>7</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
+      <c r="A78" t="s">
+        <v>138</v>
+      </c>
+      <c r="B78" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D78" t="s">
+        <v>7</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
+      <c r="A79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B79" t="s">
+        <v>130</v>
+      </c>
+      <c r="C79" t="s">
+        <v>7</v>
+      </c>
+      <c r="D79" t="s">
+        <v>164</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
+      <c r="A80" t="s">
+        <v>140</v>
+      </c>
+      <c r="B80" t="s">
+        <v>141</v>
+      </c>
+      <c r="C80" t="s">
+        <v>7</v>
+      </c>
+      <c r="D80" t="s">
+        <v>7</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
+      <c r="A81" t="s">
+        <v>27</v>
+      </c>
+      <c r="B81" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="D81" t="s">
+        <v>7</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
+      <c r="A82" t="s">
+        <v>168</v>
+      </c>
+      <c r="B82" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D82" t="s">
+        <v>169</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
+      <c r="A83" t="s">
+        <v>170</v>
+      </c>
+      <c r="B83" t="s">
+        <v>22</v>
+      </c>
+      <c r="C83" t="s">
+        <v>7</v>
+      </c>
+      <c r="D83" t="s">
+        <v>171</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
+      <c r="A84" t="s">
+        <v>172</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" t="s">
+        <v>7</v>
+      </c>
+      <c r="D84" t="s">
+        <v>173</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
+      <c r="A85" t="s">
+        <v>174</v>
+      </c>
+      <c r="B85" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
+      </c>
+      <c r="D85" t="s">
+        <v>7</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C27" r:id="rId1" display="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card" tooltip="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://lifafa-team.webflow.io/workperx" tooltip="https://lifafa-team.webflow.io/workperx"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://lifafa-team.webflow.io/workperx" tooltip="https://lifafa-team.webflow.io/workperx"/>
+    <hyperlink ref="C6" r:id="rId3" display="dummyuser@lifafa.com" tooltip="mailto:dummyuser@lifafa.com"/>
+    <hyperlink ref="C5" r:id="rId4" display="no value"/>
+    <hyperlink ref="C61" r:id="rId5" display="Nikhil.kumar@lifafa.com"/>
+    <hyperlink ref="C78" r:id="rId1" display="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card" tooltip="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card"/>
+    <hyperlink ref="C82" r:id="rId6" display="https://store.lifafa.team/inbom240400012s02/myaccount"/>
+    <hyperlink ref="C49" r:id="rId1" display="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card" tooltip="https://store.lifafa.team/inbom240400012s02/myaccount/gift-card"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="26.9375" customWidth="1"/>
+    <col min="2" max="2" width="12.375" customWidth="1"/>
+    <col min="3" max="3" width="58.125" customWidth="1"/>
+    <col min="4" max="4" width="24.8125" customWidth="1"/>
+    <col min="5" max="5" width="8.5625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>42</v>
+      </c>
+      <c r="B17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>129</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" t="s">
+        <v>131</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>134</v>
+      </c>
+      <c r="B21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D23" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>163</v>
+      </c>
+      <c r="B24" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="s">
+        <v>164</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" t="s">
+        <v>141</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>168</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>170</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="s">
+        <v>171</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>172</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>173</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
+        <v>175</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C23" r:id="rId1" display="https://store.lifafa.team/inbom240400012s05/myaccount/gift-card" tooltip="https://store.lifafa.team/inbom240400012s05/myaccount/gift-card"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://lifafa-team.webflow.io/phonepe-apple-store" tooltip="https://lifafa-team.webflow.io/phonepe-apple-store"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://lifafa-team.webflow.io/phonepe-apple-store" tooltip="https://lifafa-team.webflow.io/phonepe-apple-store"/>
+    <hyperlink ref="C9" r:id="rId3" display="https://portal.lifafa.team/store/inbom240400012s05/home"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>